--- a/Data/Output/mountains_first_ascent_demo.xlsx
+++ b/Data/Output/mountains_first_ascent_demo.xlsx
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9956</v>
+        <v>5454</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7737</v>
+        <v>6965</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8257</v>
+        <v>6158</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -1808,11 +1808,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[web_search_extract] Значення з пошукової видачі; контрольне значення відкинуто (Не розпізнано дату: «18 травня 1956 року»)</t>
+          <t>[web_search_extract] Значення з пошукової видачі; підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7644</v>
+        <v>5540</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -1857,11 +1857,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[web_search_extract] Значення з пошукової видачі; контрольне значення відкинуто (Не розпізнано дату: «15 травня 1955 року»)</t>
+          <t>[web_search_extract] Значення з пошукової видачі; підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6871</v>
+        <v>5578</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1906,11 +1906,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[web_search_extract] Значення з пошукової видачі; контрольне значення відкинуто (Не розпізнано дату: «19 жовтня 1954»)</t>
+          <t>[web_search_extract] Значення з пошукової видачі; підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>8784</v>
+        <v>6225</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -1955,11 +1955,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[web_search_extract] Значення з пошукової видачі; контрольне значення відкинуто (Не розпізнано дату: «13 травня 1960 року»)</t>
+          <t>[web_search_extract] Значення з пошукової видачі; підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8239</v>
+        <v>4853</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.himalayanrecreation.com/blog/mount-manaslu</t>
+          <t>https://www.nepaleverestbasecamp.com/blog/mount-manaslu</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6353</v>
+        <v>4361</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7586</v>
+        <v>4549</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>10162</v>
+        <v>4536</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>

--- a/Data/Output/mountains_first_ascent_demo.xlsx
+++ b/Data/Output/mountains_first_ascent_demo.xlsx
@@ -1648,7 +1648,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>first successful ascent date of Mount Everest in Nepal/China</t>
+          <t>first successful ascent date of Mount Everest in Nepal/China first ascent DD.MM.YYYY</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5454</v>
+        <v>8770</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DRlqb1VgeV7?hl=en</t>
+          <t>https://www.climbing.com/travel/k2-worlds-second-highest-mountain</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>first successful ascent date of K2 in Pakistan/China</t>
+          <t>first successful ascent date of K2 in Pakistan/China first ascent DD.MM.YYYY</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6965</v>
+        <v>6891</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>first successful ascent date of Kangchenjunga in Nepal/India</t>
+          <t>first successful ascent date of Kangchenjunga in Nepal/India first ascent DD.MM.YYYY</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6158</v>
+        <v>8072</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>first successful ascent date of Lhotse in Nepal/China</t>
+          <t>first successful ascent date of Lhotse in Nepal/China first ascent DD.MM.YYYY</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5540</v>
+        <v>8019</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -1839,12 +1839,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://globalsummitguide.com/mountains-makalu-climb-guide-nepal-tibet</t>
+          <t>https://guinnessworldrecords.com/world-records/first-ascent-of-makalu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>first successful ascent date of Makalu in Nepal/China</t>
+          <t>first successful ascent date of Makalu in Nepal/China first ascent DD.MM.YYYY</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5578</v>
+        <v>62073</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://explorersweb.com/a-brief-history-of-climbing-on-cho-oyu</t>
+          <t>https://www.summitclimb.de/en/tours/expeditions/asia/cho-oyu</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>first successful ascent date of Cho Oyu in Nepal/China</t>
+          <t>first successful ascent date of Cho Oyu in Nepal/China first ascent DD.MM.YYYY</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6225</v>
+        <v>7543</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://nepalgram.com/trip/dhaulagiri-expedition</t>
+          <t>https://www.guinnessworldrecords.com/world-records/first-ascent-of-dhaulagiri-i</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>first successful ascent date of Dhaulagiri in Nepal</t>
+          <t>first successful ascent date of Dhaulagiri in Nepal first ascent DD.MM.YYYY</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4853</v>
+        <v>7632</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.nepaleverestbasecamp.com/blog/mount-manaslu</t>
+          <t>https://en.wikipedia.org/wiki/Manaslu</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>first successful ascent date of Manaslu in Nepal</t>
+          <t>first successful ascent date of Manaslu in Nepal first ascent DD.MM.YYYY</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4361</v>
+        <v>6739</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>first successful ascent date of Nanga Parbat in Pakistan</t>
+          <t>first successful ascent date of Nanga Parbat in Pakistan first ascent DD.MM.YYYY</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4549</v>
+        <v>6621</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://nepalmountaineering.org/annapurna-day</t>
+          <t>https://tourisminfonepal.com/tag/annapurna-ascent-day/feed</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>first successful ascent date of Annapurna in Nepal</t>
+          <t>first successful ascent date of Annapurna in Nepal first ascent DD.MM.YYYY</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>4536</v>
+        <v>11919</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>

--- a/Data/Output/mountains_first_ascent_demo.xlsx
+++ b/Data/Output/mountains_first_ascent_demo.xlsx
@@ -1545,20 +1545,6 @@
   </sheetPr>
   <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="4" min="1" max="1"/>
-    <col width="16" customWidth="1" style="4" min="2" max="2"/>
-    <col width="12" customWidth="1" style="4" min="3" max="3"/>
-    <col width="8" customWidth="1" style="4" min="4" max="4"/>
-    <col width="20" customWidth="1" style="4" min="5" max="5"/>
-    <col width="46" customWidth="1" style="4" min="6" max="6"/>
-    <col width="40" customWidth="1" style="4" min="7" max="7"/>
-    <col width="8" customWidth="1" style="4" min="8" max="8"/>
-    <col width="14" customWidth="1" style="4" min="9" max="9"/>
-    <col width="60" customWidth="1" style="4" min="10" max="10"/>
-    <col width="12" customWidth="1" style="4" min="11" max="11"/>
-    <col width="10" customWidth="1" style="4" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
@@ -1661,11 +1647,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[web_search_extract] Значення з пошукової видачі; підтверджено через llm_knowledge</t>
+          <t>[web_search_extract] Значення з пошукової видачі; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>8770</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -1692,7 +1678,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.climbing.com/travel/k2-worlds-second-highest-mountain</t>
+          <t>https://en.wikipedia.org/wiki/K2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1710,11 +1696,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[web_search_extract] Значення з пошукової видачі; підтверджено через llm_knowledge</t>
+          <t>[web_search_extract] Значення з пошукової видачі; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6891</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -1741,7 +1727,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.altitudehimalaya.com/blog/kangchenjunga</t>
+          <t>https://en.wikipedia.org/wiki/Kangchenjunga</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1759,11 +1745,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[web_search_extract] Значення з пошукової видачі; підтверджено через llm_knowledge</t>
+          <t>[web_search_extract] Значення з пошукової видачі; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8072</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -1808,11 +1794,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[web_search_extract] Значення з пошукової видачі; підтверджено через llm_knowledge</t>
+          <t>[web_search_extract] Значення з пошукової видачі; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8019</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -1839,7 +1825,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://guinnessworldrecords.com/world-records/first-ascent-of-makalu</t>
+          <t>https://en.wikipedia.org/wiki/Makalu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1857,11 +1843,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[web_search_extract] Значення з пошукової видачі; підтверджено через llm_knowledge</t>
+          <t>[web_search_extract] Значення з пошукової видачі; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>62073</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1888,7 +1874,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.summitclimb.de/en/tours/expeditions/asia/cho-oyu</t>
+          <t>https://en.wikipedia.org/wiki/Cho_Oyu</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1906,11 +1892,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[web_search_extract] Значення з пошукової видачі; підтверджено через llm_knowledge</t>
+          <t>[web_search_extract] Значення з пошукової видачі; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>7543</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -1955,11 +1941,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[web_search_extract] Значення з пошукової видачі; підтверджено через llm_knowledge</t>
+          <t>[web_search_extract] Значення з пошукової видачі; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>7632</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -1986,7 +1972,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Manaslu</t>
+          <t>https://www.nepaleverestbasecamp.com/blog/mount-manaslu</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2004,11 +1990,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[web_search_extract] Значення з пошукової видачі; підтверджено через llm_knowledge</t>
+          <t>[web_search_extract] Значення з пошукової видачі; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6739</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -2035,7 +2021,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Nanga_Parbat</t>
+          <t>https://www.guinnessworldrecords.com/world-records/114053-first-ascent-of-mazeno-ridge-nanga-parbat</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2053,11 +2039,11 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[web_search_extract] Значення з пошукової видачі; підтверджено через llm_knowledge</t>
+          <t>[web_search_extract] Значення з пошукової видачі; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6621</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -2084,7 +2070,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://tourisminfonepal.com/tag/annapurna-ascent-day/feed</t>
+          <t>https://en.wikipedia.org/wiki/Annapurna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2102,11 +2088,11 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[web_search_extract] Значення з пошукової видачі; підтверджено через llm_knowledge</t>
+          <t>[web_search_extract] Значення з пошукової видачі; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>11919</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
